--- a/process_h1_hasil.xlsx
+++ b/process_h1_hasil.xlsx
@@ -5548,7 +5548,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="n">
         <v>10</v>
       </c>
@@ -5574,7 +5574,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="n">
         <v>11</v>
       </c>
@@ -5600,7 +5600,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="n">
         <v>12</v>
       </c>
@@ -5626,7 +5626,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="n">
         <v>13</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="n">
         <v>14</v>
       </c>
@@ -5678,7 +5678,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="n">
         <v>15</v>
       </c>
@@ -5704,7 +5704,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="n">
         <v>16</v>
       </c>
@@ -5730,263 +5730,263 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
+    <row r="19" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
+    <row r="20" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
+    <row r="21" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
+    <row r="22" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" s="4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
+    <row r="23" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="4" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
+    <row r="24" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
+    <row r="25" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
+    <row r="26" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
+    <row r="27" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="4" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
+    <row r="28" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="4" t="s">
         <v>153</v>
       </c>
     </row>

--- a/process_h1_hasil.xlsx
+++ b/process_h1_hasil.xlsx
@@ -5730,7 +5730,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="n">
         <v>17</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="20" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="n">
         <v>18</v>
       </c>
@@ -5782,7 +5782,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="n">
         <v>19</v>
       </c>
@@ -5808,7 +5808,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="22" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="n">
         <v>20</v>
       </c>
@@ -5834,7 +5834,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="n">
         <v>21</v>
       </c>
@@ -5860,7 +5860,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="24" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="n">
         <v>22</v>
       </c>
@@ -5886,7 +5886,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="25" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="n">
         <v>23</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="26" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="n">
         <v>24</v>
       </c>
@@ -5938,7 +5938,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="27" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="n">
         <v>25</v>
       </c>
@@ -5964,7 +5964,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="28" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="n">
         <v>26</v>
       </c>
@@ -5990,263 +5990,263 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
+    <row r="29" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="H29" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
+    <row r="30" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H30" s="4" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
+    <row r="31" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="H31" s="4" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
+    <row r="32" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H32" s="4" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
+    <row r="33" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="4" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
+    <row r="34" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H34" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
+    <row r="35" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" s="4" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="n">
+    <row r="36" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H36" s="4" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
+    <row r="37" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="H37" s="4" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
+    <row r="38" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="H38" s="4" t="s">
         <v>210</v>
       </c>
     </row>

--- a/process_h1_hasil.xlsx
+++ b/process_h1_hasil.xlsx
@@ -5990,7 +5990,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="n">
         <v>27</v>
       </c>
@@ -6016,7 +6016,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="30" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="n">
         <v>28</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="31" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="n">
         <v>29</v>
       </c>
@@ -6068,7 +6068,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="32" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="n">
         <v>30</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="33" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="n">
         <v>31</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="34" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="n">
         <v>32</v>
       </c>
@@ -6146,7 +6146,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="35" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="n">
         <v>33</v>
       </c>
@@ -6172,7 +6172,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="36" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="n">
         <v>34</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="37" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="n">
         <v>35</v>
       </c>
@@ -6224,7 +6224,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="38" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="n">
         <v>36</v>
       </c>
@@ -6250,211 +6250,211 @@
         <v>210</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
+    <row r="39" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="H39" s="4" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
+    <row r="40" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="H40" s="2" t="s">
+      <c r="H40" s="4" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
+    <row r="41" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="H41" s="2" t="s">
+      <c r="H41" s="4" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="n">
+    <row r="42" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G42" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="H42" s="4" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="n">
+    <row r="43" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="H43" s="4" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="n">
+    <row r="44" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="H44" s="4" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
+    <row r="45" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="H45" s="4" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
+    <row r="46" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G46" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="H46" s="2" t="s">
+      <c r="H46" s="4" t="s">
         <v>256</v>
       </c>
     </row>
